--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>0.08</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>0.08</v>
       </c>
       <c r="N32" t="n">
-        <v>2.41</v>
+        <v>0.12</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,22 +4907,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.75</v>
+        <v>2.17</v>
       </c>
       <c r="M60" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N60" t="n">
-        <v>1.96</v>
+        <v>3.1</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.09</v>
+        <v>1.7</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10706,10 +10706,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11131,55 +11131,55 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="M90" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N90" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA90" t="n">
         <v>2.12</v>
       </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" t="n">
-        <v>0</v>
-      </c>
-      <c r="W90" t="n">
-        <v>0</v>
-      </c>
-      <c r="X90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA90" t="n">
-        <v>2.24</v>
-      </c>
       <c r="AB90" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.67</v>
+        <v>2.9</v>
       </c>
       <c r="M92" t="n">
-        <v>4.15</v>
+        <v>3.35</v>
       </c>
       <c r="N92" t="n">
-        <v>4.7</v>
+        <v>2.35</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB92" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="M101" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="N101" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12678,10 +12678,10 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="M103" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="N103" t="n">
         <v>5.7</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13951,22 +13951,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="M115" t="n">
-        <v>3.22</v>
+        <v>5.3</v>
       </c>
       <c r="N115" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,16 +14151,16 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD115" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE115" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14395,10 +14395,10 @@
         <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="M121" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N121" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,7 +14865,7 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB121" t="n">
         <v>1.75</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,10 +18316,10 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB150" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB151" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB152" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB154" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="M158" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N158" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="M169" t="n">
-        <v>11.5</v>
+        <v>3.6</v>
       </c>
       <c r="N169" t="n">
-        <v>23</v>
+        <v>3.4</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,16 +20577,16 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC169" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD169" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE169" t="n">
         <v>0</v>
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>2.03</v>
+        <v>1.06</v>
       </c>
       <c r="M173" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="N173" t="n">
-        <v>3.35</v>
+        <v>31</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21053,16 +21053,16 @@
         <v>0</v>
       </c>
       <c r="AA173" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB173" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC173" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD173" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M175" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N175" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="M177" t="n">
         <v>3.25</v>
       </c>
       <c r="N177" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AB177" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB180" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22005,10 +22005,10 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB181" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB182" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,16 +22481,16 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB185" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC185" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD185" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE185" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G188" t="n">

--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI193"/>
+  <dimension ref="A1:AI196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="3" t="n">
-        <v>46054.34375</v>
+        <v>46054.33333333334</v>
       </c>
     </row>
     <row r="31">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46054.34375</v>
+        <v>46054.33333333334</v>
       </c>
     </row>
     <row r="32">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4417,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="AI33" s="3" t="n">
-        <v>46054.35416666666</v>
+        <v>46054.34375</v>
       </c>
     </row>
     <row r="34">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>46054.35416666666</v>
+        <v>46054.34375</v>
       </c>
     </row>
     <row r="35">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5497,27 +5497,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="AI43" s="3" t="n">
-        <v>46054.36458333334</v>
+        <v>46054.35416666666</v>
       </c>
     </row>
     <row r="44">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="AI44" s="3" t="n">
-        <v>46054.37152777778</v>
+        <v>46054.35416666666</v>
       </c>
     </row>
     <row r="45">
@@ -5735,12 +5735,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="AI45" s="3" t="n">
-        <v>46054.37152777778</v>
+        <v>46054.36458333334</v>
       </c>
     </row>
     <row r="46">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="AI48" s="3" t="n">
-        <v>46054.375</v>
+        <v>46054.37152777778</v>
       </c>
     </row>
     <row r="49">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="AI49" s="3" t="n">
-        <v>46054.375</v>
+        <v>46054.37152777778</v>
       </c>
     </row>
     <row r="50">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7035,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="AI55" s="3" t="n">
-        <v>46054.38541666666</v>
+        <v>46054.375</v>
       </c>
     </row>
     <row r="56">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7154,7 +7154,7 @@
         <v>0</v>
       </c>
       <c r="AI56" s="3" t="n">
-        <v>46054.38541666666</v>
+        <v>46054.375</v>
       </c>
     </row>
     <row r="57">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7273,7 +7273,7 @@
         <v>0</v>
       </c>
       <c r="AI57" s="3" t="n">
-        <v>46054.39583333334</v>
+        <v>46054.38541666666</v>
       </c>
     </row>
     <row r="58">
@@ -7282,12 +7282,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7392,7 +7392,7 @@
         <v>0</v>
       </c>
       <c r="AI58" s="3" t="n">
-        <v>46054.39583333334</v>
+        <v>46054.38541666666</v>
       </c>
     </row>
     <row r="59">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8106,7 +8106,7 @@
         <v>0</v>
       </c>
       <c r="AI64" s="3" t="n">
-        <v>46054.41666666666</v>
+        <v>46054.39583333334</v>
       </c>
     </row>
     <row r="65">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="AI65" s="3" t="n">
-        <v>46054.41666666666</v>
+        <v>46054.39583333334</v>
       </c>
     </row>
     <row r="66">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AI79" s="3" t="n">
-        <v>46054.4375</v>
+        <v>46054.41666666666</v>
       </c>
     </row>
     <row r="80">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10010,7 +10010,7 @@
         <v>0</v>
       </c>
       <c r="AI80" s="3" t="n">
-        <v>46054.4375</v>
+        <v>46054.41666666666</v>
       </c>
     </row>
     <row r="81">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10706,10 +10706,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11200,7 +11200,7 @@
         <v>0</v>
       </c>
       <c r="AI90" s="3" t="n">
-        <v>46054.44791666666</v>
+        <v>46054.4375</v>
       </c>
     </row>
     <row r="91">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11319,7 +11319,7 @@
         <v>0</v>
       </c>
       <c r="AI91" s="3" t="n">
-        <v>46054.45833333334</v>
+        <v>46054.4375</v>
       </c>
     </row>
     <row r="92">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="M92" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N92" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11438,7 +11438,7 @@
         <v>0</v>
       </c>
       <c r="AI92" s="3" t="n">
-        <v>46054.45833333334</v>
+        <v>46054.44791666666</v>
       </c>
     </row>
     <row r="93">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="M98" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N98" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AB98" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="M101" t="n">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="N101" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB101" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="M103" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N103" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13113,12 +13113,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13223,7 +13223,7 @@
         <v>0</v>
       </c>
       <c r="AI107" s="3" t="n">
-        <v>46054.46875</v>
+        <v>46054.45833333334</v>
       </c>
     </row>
     <row r="108">
@@ -13232,12 +13232,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13342,7 +13342,7 @@
         <v>0</v>
       </c>
       <c r="AI108" s="3" t="n">
-        <v>46054.47916666666</v>
+        <v>46054.45833333334</v>
       </c>
     </row>
     <row r="109">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13461,7 +13461,7 @@
         <v>0</v>
       </c>
       <c r="AI109" s="3" t="n">
-        <v>46054.47916666666</v>
+        <v>46054.45833333334</v>
       </c>
     </row>
     <row r="110">
@@ -13470,12 +13470,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13580,7 +13580,7 @@
         <v>0</v>
       </c>
       <c r="AI110" s="3" t="n">
-        <v>46054.47916666666</v>
+        <v>46054.46875</v>
       </c>
     </row>
     <row r="111">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13827,12 +13827,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13937,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="AI113" s="3" t="n">
-        <v>46054.5</v>
+        <v>46054.47916666666</v>
       </c>
     </row>
     <row r="114">
@@ -13946,27 +13946,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14056,7 +14056,7 @@
         <v>0</v>
       </c>
       <c r="AI114" s="3" t="n">
-        <v>46054.5</v>
+        <v>46054.47916666666</v>
       </c>
     </row>
     <row r="115">
@@ -14065,12 +14065,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,16 +14151,16 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD115" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE115" t="n">
         <v>0</v>
@@ -14175,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="AI115" s="3" t="n">
-        <v>46054.5</v>
+        <v>46054.47916666666</v>
       </c>
     </row>
     <row r="116">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>3.9</v>
+        <v>1.73</v>
       </c>
       <c r="M116" t="n">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="N116" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,16 +14389,16 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD117" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14541,12 +14541,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14651,7 +14651,7 @@
         <v>0</v>
       </c>
       <c r="AI119" s="3" t="n">
-        <v>46054.51041666666</v>
+        <v>46054.5</v>
       </c>
     </row>
     <row r="120">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14770,7 +14770,7 @@
         <v>0</v>
       </c>
       <c r="AI120" s="3" t="n">
-        <v>46054.51041666666</v>
+        <v>46054.5</v>
       </c>
     </row>
     <row r="121">
@@ -14779,27 +14779,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14868,7 +14868,7 @@
         <v>1.95</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14889,7 +14889,7 @@
         <v>0</v>
       </c>
       <c r="AI121" s="3" t="n">
-        <v>46054.51041666666</v>
+        <v>46054.5</v>
       </c>
     </row>
     <row r="122">
@@ -15017,12 +15017,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15127,7 +15127,7 @@
         <v>0</v>
       </c>
       <c r="AI123" s="3" t="n">
-        <v>46054.52083333334</v>
+        <v>46054.51041666666</v>
       </c>
     </row>
     <row r="124">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15246,7 +15246,7 @@
         <v>0</v>
       </c>
       <c r="AI124" s="3" t="n">
-        <v>46054.52083333334</v>
+        <v>46054.51041666666</v>
       </c>
     </row>
     <row r="125">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15365,7 +15365,7 @@
         <v>0</v>
       </c>
       <c r="AI125" s="3" t="n">
-        <v>46054.52083333334</v>
+        <v>46054.51041666666</v>
       </c>
     </row>
     <row r="126">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15960,7 +15960,7 @@
         <v>0</v>
       </c>
       <c r="AI130" s="3" t="n">
-        <v>46054.53125</v>
+        <v>46054.52083333334</v>
       </c>
     </row>
     <row r="131">
@@ -15969,12 +15969,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16079,7 +16079,7 @@
         <v>0</v>
       </c>
       <c r="AI131" s="3" t="n">
-        <v>46054.53125</v>
+        <v>46054.52083333334</v>
       </c>
     </row>
     <row r="132">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16198,7 +16198,7 @@
         <v>0</v>
       </c>
       <c r="AI132" s="3" t="n">
-        <v>46054.53125</v>
+        <v>46054.52083333334</v>
       </c>
     </row>
     <row r="133">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16683,12 +16683,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16793,7 +16793,7 @@
         <v>0</v>
       </c>
       <c r="AI137" s="3" t="n">
-        <v>46054.54166666666</v>
+        <v>46054.53125</v>
       </c>
     </row>
     <row r="138">
@@ -16802,12 +16802,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16912,7 +16912,7 @@
         <v>0</v>
       </c>
       <c r="AI138" s="3" t="n">
-        <v>46054.54166666666</v>
+        <v>46054.53125</v>
       </c>
     </row>
     <row r="139">
@@ -16921,12 +16921,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17031,7 +17031,7 @@
         <v>0</v>
       </c>
       <c r="AI139" s="3" t="n">
-        <v>46054.54166666666</v>
+        <v>46054.53125</v>
       </c>
     </row>
     <row r="140">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18230,12 +18230,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18316,10 +18316,10 @@
         <v>0</v>
       </c>
       <c r="AA150" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB150" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC150" t="n">
         <v>0</v>
@@ -18340,7 +18340,7 @@
         <v>0</v>
       </c>
       <c r="AI150" s="3" t="n">
-        <v>46054.55208333334</v>
+        <v>46054.54166666666</v>
       </c>
     </row>
     <row r="151">
@@ -18349,12 +18349,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB151" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18459,7 +18459,7 @@
         <v>0</v>
       </c>
       <c r="AI151" s="3" t="n">
-        <v>46054.55208333334</v>
+        <v>46054.54166666666</v>
       </c>
     </row>
     <row r="152">
@@ -18468,12 +18468,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18578,7 +18578,7 @@
         <v>0</v>
       </c>
       <c r="AI152" s="3" t="n">
-        <v>46054.55208333334</v>
+        <v>46054.54166666666</v>
       </c>
     </row>
     <row r="153">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18706,12 +18706,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB154" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18816,7 +18816,7 @@
         <v>0</v>
       </c>
       <c r="AI154" s="3" t="n">
-        <v>46054.5625</v>
+        <v>46054.55208333334</v>
       </c>
     </row>
     <row r="155">
@@ -18825,12 +18825,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18935,7 +18935,7 @@
         <v>0</v>
       </c>
       <c r="AI155" s="3" t="n">
-        <v>46054.5625</v>
+        <v>46054.55208333334</v>
       </c>
     </row>
     <row r="156">
@@ -18944,12 +18944,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19054,7 +19054,7 @@
         <v>0</v>
       </c>
       <c r="AI156" s="3" t="n">
-        <v>46054.5625</v>
+        <v>46054.55208333334</v>
       </c>
     </row>
     <row r="157">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,16 +19149,16 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD157" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,10 +19387,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -19420,12 +19420,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,10 +19506,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB160" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -19530,7 +19530,7 @@
         <v>0</v>
       </c>
       <c r="AI160" s="3" t="n">
-        <v>46054.58333333334</v>
+        <v>46054.5625</v>
       </c>
     </row>
     <row r="161">
@@ -19539,12 +19539,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19649,7 +19649,7 @@
         <v>0</v>
       </c>
       <c r="AI161" s="3" t="n">
-        <v>46054.58333333334</v>
+        <v>46054.5625</v>
       </c>
     </row>
     <row r="162">
@@ -19658,12 +19658,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,16 +19744,16 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB162" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC162" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD162" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE162" t="n">
         <v>0</v>
@@ -19768,7 +19768,7 @@
         <v>0</v>
       </c>
       <c r="AI162" s="3" t="n">
-        <v>46054.58333333334</v>
+        <v>46054.5625</v>
       </c>
     </row>
     <row r="163">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>
@@ -20253,12 +20253,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB167" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20363,7 +20363,7 @@
         <v>0</v>
       </c>
       <c r="AI167" s="3" t="n">
-        <v>46054.60416666666</v>
+        <v>46054.58333333334</v>
       </c>
     </row>
     <row r="168">
@@ -20372,12 +20372,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20482,7 +20482,7 @@
         <v>0</v>
       </c>
       <c r="AI168" s="3" t="n">
-        <v>46054.60416666666</v>
+        <v>46054.58333333334</v>
       </c>
     </row>
     <row r="169">
@@ -20491,12 +20491,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20601,7 +20601,7 @@
         <v>0</v>
       </c>
       <c r="AI169" s="3" t="n">
-        <v>46054.60416666666</v>
+        <v>46054.58333333334</v>
       </c>
     </row>
     <row r="170">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21059,10 +21059,10 @@
         <v>0</v>
       </c>
       <c r="AC173" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD173" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21205,12 +21205,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="M175" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="N175" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21291,16 +21291,16 @@
         <v>0</v>
       </c>
       <c r="AA175" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB175" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC175" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD175" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE175" t="n">
         <v>0</v>
@@ -21315,7 +21315,7 @@
         <v>0</v>
       </c>
       <c r="AI175" s="3" t="n">
-        <v>46054.625</v>
+        <v>46054.60416666666</v>
       </c>
     </row>
     <row r="176">
@@ -21324,12 +21324,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21410,10 +21410,10 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB176" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -21434,7 +21434,7 @@
         <v>0</v>
       </c>
       <c r="AI176" s="3" t="n">
-        <v>46054.625</v>
+        <v>46054.60416666666</v>
       </c>
     </row>
     <row r="177">
@@ -21443,12 +21443,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21553,7 +21553,7 @@
         <v>0</v>
       </c>
       <c r="AI177" s="3" t="n">
-        <v>46054.63541666666</v>
+        <v>46054.60416666666</v>
       </c>
     </row>
     <row r="178">
@@ -21562,12 +21562,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB178" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21672,7 +21672,7 @@
         <v>0</v>
       </c>
       <c r="AI178" s="3" t="n">
-        <v>46054.64583333334</v>
+        <v>46054.625</v>
       </c>
     </row>
     <row r="179">
@@ -21681,12 +21681,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21791,7 +21791,7 @@
         <v>0</v>
       </c>
       <c r="AI179" s="3" t="n">
-        <v>46054.65625</v>
+        <v>46054.625</v>
       </c>
     </row>
     <row r="180">
@@ -21800,12 +21800,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21886,10 +21886,10 @@
         <v>0</v>
       </c>
       <c r="AA180" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB180" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC180" t="n">
         <v>0</v>
@@ -21910,7 +21910,7 @@
         <v>0</v>
       </c>
       <c r="AI180" s="3" t="n">
-        <v>46054.66666666666</v>
+        <v>46054.63541666666</v>
       </c>
     </row>
     <row r="181">
@@ -21919,12 +21919,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22005,10 +22005,10 @@
         <v>0</v>
       </c>
       <c r="AA181" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB181" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC181" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
         <v>0</v>
       </c>
       <c r="AI181" s="3" t="n">
-        <v>46054.66666666666</v>
+        <v>46054.64583333334</v>
       </c>
     </row>
     <row r="182">
@@ -22038,12 +22038,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB182" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22148,7 +22148,7 @@
         <v>0</v>
       </c>
       <c r="AI182" s="3" t="n">
-        <v>46054.66666666666</v>
+        <v>46054.65625</v>
       </c>
     </row>
     <row r="183">
@@ -22157,12 +22157,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB183" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22267,7 +22267,7 @@
         <v>0</v>
       </c>
       <c r="AI183" s="3" t="n">
-        <v>46054.6875</v>
+        <v>46054.66666666666</v>
       </c>
     </row>
     <row r="184">
@@ -22276,12 +22276,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22386,7 +22386,7 @@
         <v>0</v>
       </c>
       <c r="AI184" s="3" t="n">
-        <v>46054.6875</v>
+        <v>46054.66666666666</v>
       </c>
     </row>
     <row r="185">
@@ -22395,12 +22395,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,16 +22481,16 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB185" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AC185" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD185" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE185" t="n">
         <v>0</v>
@@ -22505,7 +22505,7 @@
         <v>0</v>
       </c>
       <c r="AI185" s="3" t="n">
-        <v>46054.69791666666</v>
+        <v>46054.66666666666</v>
       </c>
     </row>
     <row r="186">
@@ -22514,12 +22514,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22600,10 +22600,10 @@
         <v>0</v>
       </c>
       <c r="AA186" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB186" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC186" t="n">
         <v>0</v>
@@ -22624,7 +22624,7 @@
         <v>0</v>
       </c>
       <c r="AI186" s="3" t="n">
-        <v>46054.69791666666</v>
+        <v>46054.6875</v>
       </c>
     </row>
     <row r="187">
@@ -22633,12 +22633,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22743,7 +22743,7 @@
         <v>0</v>
       </c>
       <c r="AI187" s="3" t="n">
-        <v>46054.70833333334</v>
+        <v>46054.6875</v>
       </c>
     </row>
     <row r="188">
@@ -22752,12 +22752,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22838,10 +22838,10 @@
         <v>0</v>
       </c>
       <c r="AA188" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB188" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC188" t="n">
         <v>0</v>
@@ -22862,7 +22862,7 @@
         <v>0</v>
       </c>
       <c r="AI188" s="3" t="n">
-        <v>46054.70833333334</v>
+        <v>46054.69791666666</v>
       </c>
     </row>
     <row r="189">
@@ -22871,12 +22871,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,16 +22957,16 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB189" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC189" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD189" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE189" t="n">
         <v>0</v>
@@ -22981,7 +22981,7 @@
         <v>0</v>
       </c>
       <c r="AI189" s="3" t="n">
-        <v>46054.70833333334</v>
+        <v>46054.69791666666</v>
       </c>
     </row>
     <row r="190">
@@ -22990,12 +22990,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23100,7 +23100,7 @@
         <v>0</v>
       </c>
       <c r="AI190" s="3" t="n">
-        <v>46054.72916666666</v>
+        <v>46054.70833333334</v>
       </c>
     </row>
     <row r="191">
@@ -23109,27 +23109,27 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23195,10 +23195,10 @@
         <v>0</v>
       </c>
       <c r="AA191" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB191" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC191" t="n">
         <v>0</v>
@@ -23219,7 +23219,7 @@
         <v>0</v>
       </c>
       <c r="AI191" s="3" t="n">
-        <v>46054.75</v>
+        <v>46054.70833333334</v>
       </c>
     </row>
     <row r="192">
@@ -23228,7 +23228,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23338,7 +23338,7 @@
         <v>0</v>
       </c>
       <c r="AI192" s="3" t="n">
-        <v>46054.8125</v>
+        <v>46054.70833333334</v>
       </c>
     </row>
     <row r="193">
@@ -23347,116 +23347,473 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>CD Tondela</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" t="n">
+        <v>0</v>
+      </c>
+      <c r="V193" t="n">
+        <v>0</v>
+      </c>
+      <c r="W193" t="n">
+        <v>0</v>
+      </c>
+      <c r="X193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI193" s="3" t="n">
+        <v>46054.72916666666</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Universidad Católica</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L194" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="M194" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="N194" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>0</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" t="n">
+        <v>0</v>
+      </c>
+      <c r="T194" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" t="n">
+        <v>0</v>
+      </c>
+      <c r="V194" t="n">
+        <v>0</v>
+      </c>
+      <c r="W194" t="n">
+        <v>0</v>
+      </c>
+      <c r="X194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI194" s="3" t="n">
+        <v>46054.75</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Treasure Beach</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>0</v>
+      </c>
+      <c r="R195" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" t="n">
+        <v>0</v>
+      </c>
+      <c r="T195" t="n">
+        <v>0</v>
+      </c>
+      <c r="U195" t="n">
+        <v>0</v>
+      </c>
+      <c r="V195" t="n">
+        <v>0</v>
+      </c>
+      <c r="W195" t="n">
+        <v>0</v>
+      </c>
+      <c r="X195" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI195" s="3" t="n">
+        <v>46054.8125</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="C196" t="inlineStr">
         <is>
           <t>Chile Primera División</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D196" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
+      <c r="E196" t="inlineStr">
         <is>
           <t>Palestino</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
+      <c r="F196" t="inlineStr">
         <is>
           <t>Ñublense</t>
         </is>
       </c>
-      <c r="G193" t="n">
-        <v>0</v>
-      </c>
-      <c r="H193" t="n">
-        <v>0</v>
-      </c>
-      <c r="I193" t="n">
-        <v>0</v>
-      </c>
-      <c r="J193" t="n">
-        <v>0</v>
-      </c>
-      <c r="K193" t="inlineStr">
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L193" t="n">
-        <v>0</v>
-      </c>
-      <c r="M193" t="n">
-        <v>0</v>
-      </c>
-      <c r="N193" t="n">
-        <v>0</v>
-      </c>
-      <c r="O193" t="n">
-        <v>0</v>
-      </c>
-      <c r="P193" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0</v>
-      </c>
-      <c r="S193" t="n">
-        <v>0</v>
-      </c>
-      <c r="T193" t="n">
-        <v>0</v>
-      </c>
-      <c r="U193" t="n">
-        <v>0</v>
-      </c>
-      <c r="V193" t="n">
-        <v>0</v>
-      </c>
-      <c r="W193" t="n">
-        <v>0</v>
-      </c>
-      <c r="X193" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y193" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA193" t="n">
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>0</v>
+      </c>
+      <c r="R196" t="n">
+        <v>0</v>
+      </c>
+      <c r="S196" t="n">
+        <v>0</v>
+      </c>
+      <c r="T196" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" t="n">
+        <v>0</v>
+      </c>
+      <c r="V196" t="n">
+        <v>0</v>
+      </c>
+      <c r="W196" t="n">
+        <v>0</v>
+      </c>
+      <c r="X196" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA196" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB193" t="n">
+      <c r="AB196" t="n">
         <v>2.07</v>
       </c>
-      <c r="AC193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH193" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI193" s="3" t="n">
+      <c r="AC196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI196" s="3" t="n">
         <v>46054.85416666666</v>
       </c>
     </row>

--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,22 +5502,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N65" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11182,10 +11182,10 @@
         <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="M96" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N96" t="n">
-        <v>2.35</v>
+        <v>3.8</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="M109" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N109" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AB109" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="M117" t="n">
-        <v>5.3</v>
+        <v>3.22</v>
       </c>
       <c r="N117" t="n">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,16 +14389,16 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,16 +14508,16 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC118" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD118" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE118" t="n">
         <v>0</v>
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,22 +14784,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="M153" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N153" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB154" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,16 +19149,16 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC157" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD157" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,10 +19387,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>4.4</v>
+        <v>1.78</v>
       </c>
       <c r="M160" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N160" t="n">
-        <v>1.72</v>
+        <v>4.3</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,10 +19506,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AB160" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB161" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,16 +19744,16 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD162" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB167" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,10 +20458,10 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20821,10 +20821,10 @@
         <v>0</v>
       </c>
       <c r="AC171" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD171" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21053,10 +21053,10 @@
         <v>0</v>
       </c>
       <c r="AA173" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB173" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21297,10 +21297,10 @@
         <v>0</v>
       </c>
       <c r="AC175" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD175" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21410,10 +21410,10 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB176" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>6.9</v>
+        <v>5.3</v>
       </c>
       <c r="M188" t="n">
         <v>4.4</v>
       </c>
       <c r="N188" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22838,16 +22838,16 @@
         <v>0</v>
       </c>
       <c r="AA188" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB188" t="n">
-        <v>1.85</v>
+        <v>2.34</v>
       </c>
       <c r="AC188" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD188" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5.3</v>
+        <v>6.9</v>
       </c>
       <c r="M189" t="n">
         <v>4.4</v>
       </c>
       <c r="N189" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,16 +22957,16 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB189" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="AC189" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD189" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE189" t="n">
         <v>0</v>

--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="M65" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N65" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11182,10 +11182,10 @@
         <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD90" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE90" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="M100" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="N100" t="n">
-        <v>3.21</v>
+        <v>2.35</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="M103" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N103" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="M106" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="N106" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="M118" t="n">
-        <v>5.3</v>
+        <v>3.22</v>
       </c>
       <c r="N118" t="n">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,16 +14508,16 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE118" t="n">
         <v>0</v>
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.9</v>
+        <v>1.25</v>
       </c>
       <c r="M121" t="n">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="N121" t="n">
-        <v>1.9</v>
+        <v>12.5</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="M154" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N154" t="n">
-        <v>5.1</v>
+        <v>4.12</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="M156" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N156" t="n">
-        <v>4.12</v>
+        <v>3.55</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.25</v>
+        <v>4.4</v>
       </c>
       <c r="M157" t="n">
-        <v>6.1</v>
+        <v>4.1</v>
       </c>
       <c r="N157" t="n">
-        <v>11</v>
+        <v>1.72</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,16 +19149,16 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AB157" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC157" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD157" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,16 +19268,16 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC158" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD158" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE158" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,10 +19506,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB162" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,10 +20458,10 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20821,10 +20821,10 @@
         <v>0</v>
       </c>
       <c r="AC171" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD171" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21053,10 +21053,10 @@
         <v>0</v>
       </c>
       <c r="AA173" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB173" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC173" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21297,10 +21297,10 @@
         <v>0</v>
       </c>
       <c r="AC175" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD175" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21410,10 +21410,10 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB176" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB179" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="M185" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N185" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB185" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5.3</v>
+        <v>6.9</v>
       </c>
       <c r="M188" t="n">
         <v>4.4</v>
       </c>
       <c r="N188" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22838,16 +22838,16 @@
         <v>0</v>
       </c>
       <c r="AA188" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB188" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="AC188" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD188" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>6.9</v>
+        <v>5.3</v>
       </c>
       <c r="M189" t="n">
         <v>4.4</v>
       </c>
       <c r="N189" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,16 +22957,16 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB189" t="n">
-        <v>1.85</v>
+        <v>2.34</v>
       </c>
       <c r="AC189" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD189" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G191" t="n">

--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="M103" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N103" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,16 +14389,16 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC117" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD117" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="M121" t="n">
-        <v>5.3</v>
+        <v>3.22</v>
       </c>
       <c r="N121" t="n">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="M155" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N155" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AB155" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="M158" t="n">
-        <v>6.1</v>
+        <v>3.65</v>
       </c>
       <c r="N158" t="n">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,16 +19268,16 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AB158" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC158" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,16 +19387,16 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC159" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD159" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB161" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,10 +20458,10 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB172" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21178,10 +21178,10 @@
         <v>0</v>
       </c>
       <c r="AC174" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD174" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21297,10 +21297,10 @@
         <v>0</v>
       </c>
       <c r="AC175" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD175" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21410,10 +21410,10 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB176" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB178" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB183" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB185" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>6.9</v>
+        <v>5.3</v>
       </c>
       <c r="M188" t="n">
         <v>4.4</v>
       </c>
       <c r="N188" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22838,16 +22838,16 @@
         <v>0</v>
       </c>
       <c r="AA188" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB188" t="n">
-        <v>1.85</v>
+        <v>2.34</v>
       </c>
       <c r="AC188" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD188" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5.3</v>
+        <v>6.9</v>
       </c>
       <c r="M189" t="n">
         <v>4.4</v>
       </c>
       <c r="N189" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,16 +22957,16 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB189" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="AC189" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD189" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE189" t="n">
         <v>0</v>

--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="N37" t="n">
-        <v>4.9</v>
+        <v>2.73</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.85</v>
+        <v>2.17</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N63" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10468,10 +10468,10 @@
         <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="M93" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="N93" t="n">
-        <v>2.42</v>
+        <v>3.55</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="M97" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N97" t="n">
-        <v>2.35</v>
+        <v>5.7</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.67</v>
+        <v>2.9</v>
       </c>
       <c r="M102" t="n">
-        <v>4.15</v>
+        <v>3.35</v>
       </c>
       <c r="N102" t="n">
-        <v>4.7</v>
+        <v>2.35</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB102" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="M108" t="n">
-        <v>3.75</v>
+        <v>3.46</v>
       </c>
       <c r="N108" t="n">
-        <v>3.8</v>
+        <v>2.32</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="M109" t="n">
         <v>3.4</v>
       </c>
       <c r="N109" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>3.9</v>
+        <v>1.73</v>
       </c>
       <c r="M116" t="n">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="N116" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,16 +14389,16 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AB117" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AC117" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,16 +14508,16 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AC118" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD118" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.73</v>
+        <v>3.9</v>
       </c>
       <c r="M121" t="n">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="N121" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15823,10 +15823,10 @@
         <v>0</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD129" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="M155" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N155" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AB155" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,16 +19149,16 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC157" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD157" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.78</v>
+        <v>4.4</v>
       </c>
       <c r="M158" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N158" t="n">
-        <v>4.3</v>
+        <v>1.72</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,16 +19387,16 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD159" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>4.4</v>
+        <v>1.78</v>
       </c>
       <c r="M161" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N161" t="n">
-        <v>1.72</v>
+        <v>4.3</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AB161" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20101,10 +20101,10 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB165" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,10 +20458,10 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20696,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB170" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21178,10 +21178,10 @@
         <v>0</v>
       </c>
       <c r="AC174" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD174" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21297,10 +21297,10 @@
         <v>0</v>
       </c>
       <c r="AC175" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD175" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE175" t="n">
         <v>0</v>
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>

--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.11</v>
+        <v>1.9</v>
       </c>
       <c r="M46" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="N46" t="n">
-        <v>2.09</v>
+        <v>3.45</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="M47" t="n">
-        <v>3.54</v>
+        <v>4.77</v>
       </c>
       <c r="N47" t="n">
-        <v>3.45</v>
+        <v>6.92</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="M64" t="n">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10468,10 +10468,10 @@
         <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10587,10 +10587,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="M97" t="n">
-        <v>3.75</v>
+        <v>3.46</v>
       </c>
       <c r="N97" t="n">
-        <v>5.7</v>
+        <v>2.32</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="M99" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="N99" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.8</v>
+        <v>2.34</v>
       </c>
       <c r="M108" t="n">
-        <v>3.46</v>
+        <v>3.62</v>
       </c>
       <c r="N108" t="n">
-        <v>2.32</v>
+        <v>3.21</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="M116" t="n">
-        <v>3.22</v>
+        <v>5.3</v>
       </c>
       <c r="N116" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,16 +14270,16 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC116" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD116" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE116" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.25</v>
+        <v>4.02</v>
       </c>
       <c r="M118" t="n">
-        <v>5.3</v>
+        <v>3.41</v>
       </c>
       <c r="N118" t="n">
-        <v>12.5</v>
+        <v>1.85</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,16 +14508,16 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AC118" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>4.02</v>
+        <v>3.9</v>
       </c>
       <c r="M119" t="n">
-        <v>3.41</v>
+        <v>3.55</v>
       </c>
       <c r="N119" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="M155" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N155" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AB155" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="M156" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N156" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AB156" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,16 +19149,16 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD157" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,10 +19387,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="M161" t="n">
-        <v>3.65</v>
+        <v>6.1</v>
       </c>
       <c r="N161" t="n">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,16 +19625,16 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AB161" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC161" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD161" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB162" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20101,10 +20101,10 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21297,10 +21297,10 @@
         <v>0</v>
       </c>
       <c r="AC175" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD175" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE175" t="n">
         <v>0</v>
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21535,10 +21535,10 @@
         <v>0</v>
       </c>
       <c r="AC177" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD177" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB179" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="M183" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N183" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22362,10 +22362,10 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB184" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5.3</v>
+        <v>6.9</v>
       </c>
       <c r="M188" t="n">
         <v>4.4</v>
       </c>
       <c r="N188" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22838,16 +22838,16 @@
         <v>0</v>
       </c>
       <c r="AA188" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB188" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="AC188" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD188" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>6.9</v>
+        <v>5.3</v>
       </c>
       <c r="M189" t="n">
         <v>4.4</v>
       </c>
       <c r="N189" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,16 +22957,16 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB189" t="n">
-        <v>1.85</v>
+        <v>2.34</v>
       </c>
       <c r="AC189" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD189" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE189" t="n">
         <v>0</v>

--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.33</v>
+        <v>2.65</v>
       </c>
       <c r="M32" t="n">
-        <v>3.91</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="M38" t="n">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>4.23</v>
+        <v>4.9</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="M40" t="n">
-        <v>3.22</v>
+        <v>3.84</v>
       </c>
       <c r="N40" t="n">
-        <v>2.73</v>
+        <v>4.23</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="M46" t="n">
-        <v>3.54</v>
+        <v>4.77</v>
       </c>
       <c r="N46" t="n">
-        <v>3.45</v>
+        <v>6.92</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>4.77</v>
+        <v>3.54</v>
       </c>
       <c r="N47" t="n">
-        <v>6.92</v>
+        <v>3.45</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="M63" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>3.53</v>
       </c>
       <c r="N64" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10111,10 +10111,10 @@
         <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10587,10 +10587,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="M97" t="n">
-        <v>3.46</v>
+        <v>3.75</v>
       </c>
       <c r="N97" t="n">
-        <v>2.32</v>
+        <v>5.7</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="M103" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="N103" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="M105" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N105" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,16 +14270,16 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AB116" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AC116" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD116" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE116" t="n">
         <v>0</v>
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>3.9</v>
+        <v>1.73</v>
       </c>
       <c r="M119" t="n">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="N119" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="M120" t="n">
-        <v>3.22</v>
+        <v>5.3</v>
       </c>
       <c r="N120" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,16 +14746,16 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD120" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15823,10 +15823,10 @@
         <v>0</v>
       </c>
       <c r="AC129" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD129" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15942,10 +15942,10 @@
         <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD130" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>4.4</v>
+        <v>1.25</v>
       </c>
       <c r="M159" t="n">
-        <v>4.1</v>
+        <v>6.1</v>
       </c>
       <c r="N159" t="n">
-        <v>1.72</v>
+        <v>11</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,16 +19387,16 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AB159" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AC159" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD159" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.25</v>
+        <v>4.4</v>
       </c>
       <c r="M161" t="n">
-        <v>6.1</v>
+        <v>4.1</v>
       </c>
       <c r="N161" t="n">
-        <v>11</v>
+        <v>1.72</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,16 +19625,16 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AB161" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC161" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD161" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE161" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB166" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20696,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB170" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB172" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21178,10 +21178,10 @@
         <v>0</v>
       </c>
       <c r="AC174" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD174" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE174" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21535,10 +21535,10 @@
         <v>0</v>
       </c>
       <c r="AC177" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD177" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB178" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="M183" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N183" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB183" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22362,10 +22362,10 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB184" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>6.9</v>
+        <v>5.3</v>
       </c>
       <c r="M188" t="n">
         <v>4.4</v>
       </c>
       <c r="N188" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22838,16 +22838,16 @@
         <v>0</v>
       </c>
       <c r="AA188" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB188" t="n">
-        <v>1.85</v>
+        <v>2.34</v>
       </c>
       <c r="AC188" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD188" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5.3</v>
+        <v>6.9</v>
       </c>
       <c r="M189" t="n">
         <v>4.4</v>
       </c>
       <c r="N189" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,16 +22957,16 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB189" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="AC189" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD189" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE189" t="n">
         <v>0</v>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G192" t="n">

--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.65</v>
+        <v>4.33</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.91</v>
       </c>
       <c r="N32" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.34</v>
+        <v>3.11</v>
       </c>
       <c r="M46" t="n">
-        <v>4.77</v>
+        <v>3.34</v>
       </c>
       <c r="N46" t="n">
-        <v>6.92</v>
+        <v>2.09</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.11</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="N49" t="n">
-        <v>2.09</v>
+        <v>3.45</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="M62" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10111,10 +10111,10 @@
         <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11063,10 +11063,10 @@
         <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="M97" t="n">
-        <v>3.75</v>
+        <v>3.46</v>
       </c>
       <c r="N97" t="n">
-        <v>5.7</v>
+        <v>2.32</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.9</v>
+        <v>3.45</v>
       </c>
       <c r="M100" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="N100" t="n">
-        <v>3.8</v>
+        <v>2.09</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="M102" t="n">
         <v>3.4</v>
       </c>
       <c r="N102" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="M109" t="n">
-        <v>3.28</v>
+        <v>2.99</v>
       </c>
       <c r="N109" t="n">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,55 +14463,55 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB118" t="n">
         <v>1.85</v>
-      </c>
-      <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" t="n">
-        <v>0</v>
-      </c>
-      <c r="V118" t="n">
-        <v>0</v>
-      </c>
-      <c r="W118" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA118" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB118" t="n">
-        <v>1.77</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="M119" t="n">
-        <v>3.22</v>
+        <v>5.3</v>
       </c>
       <c r="N119" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,16 +14627,16 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD119" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.25</v>
+        <v>4.02</v>
       </c>
       <c r="M120" t="n">
-        <v>5.3</v>
+        <v>3.41</v>
       </c>
       <c r="N120" t="n">
-        <v>12.5</v>
+        <v>1.85</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,16 +14746,16 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AC120" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15942,10 +15942,10 @@
         <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16180,10 +16180,10 @@
         <v>0</v>
       </c>
       <c r="AC132" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD132" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE132" t="n">
         <v>0</v>
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="M154" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N154" t="n">
-        <v>4.12</v>
+        <v>3.55</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,16 +19268,16 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC158" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD158" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="M159" t="n">
-        <v>6.1</v>
+        <v>3.65</v>
       </c>
       <c r="N159" t="n">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,16 +19387,16 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AB159" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC159" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD159" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19863,10 +19863,10 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB163" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20101,10 +20101,10 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB165" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20702,10 +20702,10 @@
         <v>0</v>
       </c>
       <c r="AC170" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD170" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB171" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21178,10 +21178,10 @@
         <v>0</v>
       </c>
       <c r="AC174" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD174" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB179" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22362,10 +22362,10 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB184" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G192" t="n">

--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.33</v>
+        <v>2.65</v>
       </c>
       <c r="M32" t="n">
-        <v>3.91</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="M40" t="n">
-        <v>3.84</v>
+        <v>3.22</v>
       </c>
       <c r="N40" t="n">
-        <v>4.23</v>
+        <v>2.73</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="M48" t="n">
-        <v>4.77</v>
+        <v>3.54</v>
       </c>
       <c r="N48" t="n">
-        <v>6.92</v>
+        <v>3.45</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.9</v>
+        <v>3.11</v>
       </c>
       <c r="M49" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="N49" t="n">
-        <v>3.45</v>
+        <v>2.09</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N62" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="M66" t="n">
-        <v>3.59</v>
+        <v>4.01</v>
       </c>
       <c r="N66" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.81</v>
+        <v>2.52</v>
       </c>
       <c r="M89" t="n">
-        <v>4.17</v>
+        <v>3.64</v>
       </c>
       <c r="N89" t="n">
-        <v>4.01</v>
+        <v>2.7</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,16 +11057,16 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC89" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE89" t="n">
         <v>0</v>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.52</v>
+        <v>1.81</v>
       </c>
       <c r="M90" t="n">
-        <v>3.64</v>
+        <v>4.17</v>
       </c>
       <c r="N90" t="n">
-        <v>2.7</v>
+        <v>4.01</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,16 +11176,16 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE90" t="n">
         <v>0</v>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="M93" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N93" t="n">
-        <v>5.7</v>
+        <v>2.35</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="M96" t="n">
-        <v>6.4</v>
+        <v>4.15</v>
       </c>
       <c r="N96" t="n">
-        <v>12</v>
+        <v>4.7</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="M97" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="N97" t="n">
-        <v>2.32</v>
+        <v>2.9</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="M100" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="N100" t="n">
-        <v>2.09</v>
+        <v>3.8</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.67</v>
+        <v>2.34</v>
       </c>
       <c r="M103" t="n">
-        <v>4.15</v>
+        <v>3.62</v>
       </c>
       <c r="N103" t="n">
-        <v>4.7</v>
+        <v>3.21</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="M104" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="N104" t="n">
-        <v>3.55</v>
+        <v>2.32</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="M107" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="N107" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="M108" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N108" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AB108" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.7</v>
+        <v>2.59</v>
       </c>
       <c r="M111" t="n">
-        <v>4.1</v>
+        <v>3.32</v>
       </c>
       <c r="N111" t="n">
-        <v>4.5</v>
+        <v>2.36</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AB111" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="M154" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N154" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AB154" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="M156" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N156" t="n">
-        <v>5.1</v>
+        <v>4.12</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>4.4</v>
+        <v>1.25</v>
       </c>
       <c r="M157" t="n">
-        <v>4.1</v>
+        <v>6.1</v>
       </c>
       <c r="N157" t="n">
-        <v>1.72</v>
+        <v>11</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,16 +19149,16 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AB157" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AC157" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD157" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="M158" t="n">
-        <v>6.1</v>
+        <v>3.65</v>
       </c>
       <c r="N158" t="n">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,16 +19268,16 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AB158" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC158" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,10 +19387,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB161" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19863,10 +19863,10 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC163" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20101,10 +20101,10 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB167" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20702,10 +20702,10 @@
         <v>0</v>
       </c>
       <c r="AC170" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD170" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>2</v>
+        <v>1.06</v>
       </c>
       <c r="M171" t="n">
-        <v>3.6</v>
+        <v>11.5</v>
       </c>
       <c r="N171" t="n">
-        <v>3.4</v>
+        <v>31</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,16 +20815,16 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB171" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC171" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD171" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB172" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB178" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="M179" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="N179" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB182" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5.3</v>
+        <v>6.9</v>
       </c>
       <c r="M188" t="n">
         <v>4.4</v>
       </c>
       <c r="N188" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22838,16 +22838,16 @@
         <v>0</v>
       </c>
       <c r="AA188" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB188" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="AC188" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD188" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>6.9</v>
+        <v>5.3</v>
       </c>
       <c r="M189" t="n">
         <v>4.4</v>
       </c>
       <c r="N189" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,16 +22957,16 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB189" t="n">
-        <v>1.85</v>
+        <v>2.34</v>
       </c>
       <c r="AC189" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD189" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE189" t="n">
         <v>0</v>
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23314,10 +23314,10 @@
         <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB192" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>

--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.65</v>
+        <v>4.33</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.91</v>
       </c>
       <c r="N32" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.17</v>
+        <v>3.05</v>
       </c>
       <c r="M62" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="N62" t="n">
-        <v>3.1</v>
+        <v>2.18</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10825,10 +10825,10 @@
         <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE87" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="M89" t="n">
-        <v>3.64</v>
+        <v>2.81</v>
       </c>
       <c r="N89" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.81</v>
+        <v>2.52</v>
       </c>
       <c r="M90" t="n">
-        <v>4.17</v>
+        <v>3.64</v>
       </c>
       <c r="N90" t="n">
-        <v>4.01</v>
+        <v>2.7</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,16 +11176,16 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD90" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="M93" t="n">
-        <v>3.35</v>
+        <v>4.15</v>
       </c>
       <c r="N93" t="n">
-        <v>2.35</v>
+        <v>4.7</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="M94" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N94" t="n">
-        <v>5.7</v>
+        <v>2.35</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="M96" t="n">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="N96" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M97" t="n">
         <v>3.4</v>
       </c>
       <c r="N97" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="M100" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N100" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AB100" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="M101" t="n">
-        <v>3.28</v>
+        <v>2.99</v>
       </c>
       <c r="N101" t="n">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="M107" t="n">
-        <v>2.99</v>
+        <v>6.4</v>
       </c>
       <c r="N107" t="n">
-        <v>2.42</v>
+        <v>12</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.1</v>
+        <v>3.45</v>
       </c>
       <c r="M108" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="N108" t="n">
-        <v>3.55</v>
+        <v>2.09</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="M116" t="n">
-        <v>3.22</v>
+        <v>5.3</v>
       </c>
       <c r="N116" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,16 +14270,16 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC116" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD116" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE116" t="n">
         <v>0</v>
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,22 +14427,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.25</v>
+        <v>3.9</v>
       </c>
       <c r="M119" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="N119" t="n">
-        <v>12.5</v>
+        <v>1.9</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,16 +14627,16 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AC119" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>4.02</v>
+        <v>1.73</v>
       </c>
       <c r="M120" t="n">
-        <v>3.41</v>
+        <v>3.22</v>
       </c>
       <c r="N120" t="n">
-        <v>1.85</v>
+        <v>4.7</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.9</v>
+        <v>4.02</v>
       </c>
       <c r="M121" t="n">
-        <v>3.55</v>
+        <v>3.41</v>
       </c>
       <c r="N121" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="M128" t="n">
-        <v>3.68</v>
+        <v>3.39</v>
       </c>
       <c r="N128" t="n">
-        <v>4.12</v>
+        <v>2.73</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15823,10 +15823,10 @@
         <v>0</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD129" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.7</v>
+        <v>1.38</v>
       </c>
       <c r="M131" t="n">
-        <v>3.39</v>
+        <v>4.3</v>
       </c>
       <c r="N131" t="n">
-        <v>2.73</v>
+        <v>9.5</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16180,10 +16180,10 @@
         <v>0</v>
       </c>
       <c r="AC132" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD132" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="M154" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N154" t="n">
-        <v>5.1</v>
+        <v>4.12</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="M156" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N156" t="n">
-        <v>4.12</v>
+        <v>5.1</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.25</v>
+        <v>4.4</v>
       </c>
       <c r="M157" t="n">
-        <v>6.1</v>
+        <v>4.1</v>
       </c>
       <c r="N157" t="n">
-        <v>11</v>
+        <v>1.72</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,16 +19149,16 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AB157" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC157" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD157" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="M158" t="n">
-        <v>3.65</v>
+        <v>6.1</v>
       </c>
       <c r="N158" t="n">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,16 +19268,16 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC158" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD158" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE158" t="n">
         <v>0</v>
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>4.4</v>
+        <v>1.78</v>
       </c>
       <c r="M161" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N161" t="n">
-        <v>1.72</v>
+        <v>4.3</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AB161" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20101,10 +20101,10 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB165" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="M174" t="n">
-        <v>4.69</v>
+        <v>3.6</v>
       </c>
       <c r="N174" t="n">
-        <v>5.97</v>
+        <v>3.4</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21172,10 +21172,10 @@
         <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB174" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>2.32</v>
+        <v>1.51</v>
       </c>
       <c r="M176" t="n">
-        <v>3.13</v>
+        <v>4.69</v>
       </c>
       <c r="N176" t="n">
-        <v>3.44</v>
+        <v>5.97</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="M183" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N183" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB183" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22362,10 +22362,10 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB184" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23076,10 +23076,10 @@
         <v>0</v>
       </c>
       <c r="AA190" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB190" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC190" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23314,10 +23314,10 @@
         <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB192" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>

--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,22 +5502,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.11</v>
+        <v>1.34</v>
       </c>
       <c r="M46" t="n">
-        <v>3.34</v>
+        <v>4.77</v>
       </c>
       <c r="N46" t="n">
-        <v>2.09</v>
+        <v>6.92</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>4.77</v>
+        <v>3.54</v>
       </c>
       <c r="N47" t="n">
-        <v>6.92</v>
+        <v>3.45</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.85</v>
+        <v>2.17</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N61" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10825,10 +10825,10 @@
         <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.52</v>
+        <v>1.81</v>
       </c>
       <c r="M90" t="n">
-        <v>3.64</v>
+        <v>4.17</v>
       </c>
       <c r="N90" t="n">
-        <v>2.7</v>
+        <v>4.01</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,16 +11176,16 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE90" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="M93" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="N93" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AB93" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="M94" t="n">
-        <v>3.35</v>
+        <v>4.15</v>
       </c>
       <c r="N94" t="n">
-        <v>2.35</v>
+        <v>4.7</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="M96" t="n">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="N96" t="n">
-        <v>3.8</v>
+        <v>12</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="M100" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="N100" t="n">
-        <v>2.9</v>
+        <v>2.09</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.34</v>
+        <v>1.6</v>
       </c>
       <c r="M102" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="N102" t="n">
-        <v>3.21</v>
+        <v>5.7</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="M108" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="N108" t="n">
-        <v>2.09</v>
+        <v>3.8</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.6</v>
+        <v>2.34</v>
       </c>
       <c r="M109" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="N109" t="n">
-        <v>5.7</v>
+        <v>3.21</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.7</v>
+        <v>2.59</v>
       </c>
       <c r="M115" t="n">
-        <v>4.1</v>
+        <v>3.32</v>
       </c>
       <c r="N115" t="n">
-        <v>4.5</v>
+        <v>2.36</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AB115" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>3.9</v>
+        <v>1.73</v>
       </c>
       <c r="M119" t="n">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="N119" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>4.02</v>
+        <v>3.9</v>
       </c>
       <c r="M121" t="n">
-        <v>3.41</v>
+        <v>3.55</v>
       </c>
       <c r="N121" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.13</v>
+        <v>3.35</v>
       </c>
       <c r="M125" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="N125" t="n">
-        <v>3.76</v>
+        <v>2.15</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15823,10 +15823,10 @@
         <v>0</v>
       </c>
       <c r="AC129" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD129" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15942,10 +15942,10 @@
         <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD130" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>4.33</v>
+        <v>1.99</v>
       </c>
       <c r="M153" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="N153" t="n">
-        <v>1.85</v>
+        <v>4.12</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.99</v>
+        <v>4.33</v>
       </c>
       <c r="M154" t="n">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="N154" t="n">
-        <v>4.12</v>
+        <v>1.85</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,16 +19268,16 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,16 +19387,16 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC159" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD159" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,10 +19506,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB160" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.78</v>
+        <v>4.4</v>
       </c>
       <c r="M161" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N161" t="n">
-        <v>4.3</v>
+        <v>1.72</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AB161" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB164" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB167" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20702,10 +20702,10 @@
         <v>0</v>
       </c>
       <c r="AC170" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD170" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20821,10 +20821,10 @@
         <v>0</v>
       </c>
       <c r="AC171" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD171" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="M174" t="n">
-        <v>3.6</v>
+        <v>4.69</v>
       </c>
       <c r="N174" t="n">
-        <v>3.4</v>
+        <v>5.97</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21172,10 +21172,10 @@
         <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB174" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB177" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23076,10 +23076,10 @@
         <v>0</v>
       </c>
       <c r="AA190" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB190" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC190" t="n">
         <v>0</v>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23195,10 +23195,10 @@
         <v>0</v>
       </c>
       <c r="AA191" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB191" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC191" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G192" t="n">

--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,22 +5502,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>3.11</v>
       </c>
       <c r="M47" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="N47" t="n">
-        <v>3.45</v>
+        <v>2.09</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.11</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="N49" t="n">
-        <v>2.09</v>
+        <v>3.45</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="M60" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.85</v>
+        <v>2.17</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N64" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="M95" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="N95" t="n">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.2</v>
+        <v>2.45</v>
       </c>
       <c r="M96" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="N96" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3.45</v>
+        <v>2.34</v>
       </c>
       <c r="M100" t="n">
-        <v>3.28</v>
+        <v>3.62</v>
       </c>
       <c r="N100" t="n">
-        <v>2.09</v>
+        <v>3.21</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.6</v>
+        <v>3.45</v>
       </c>
       <c r="M102" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="N102" t="n">
-        <v>5.7</v>
+        <v>2.09</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="M103" t="n">
-        <v>3.46</v>
+        <v>4.15</v>
       </c>
       <c r="N103" t="n">
-        <v>2.32</v>
+        <v>4.7</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="M106" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N106" t="n">
-        <v>2.35</v>
+        <v>5.7</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="M109" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="N109" t="n">
-        <v>3.21</v>
+        <v>2.35</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,16 +14270,16 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD116" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE116" t="n">
         <v>0</v>
@@ -14308,22 +14308,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>4.02</v>
+        <v>3.9</v>
       </c>
       <c r="M118" t="n">
-        <v>3.41</v>
+        <v>3.55</v>
       </c>
       <c r="N118" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="M119" t="n">
-        <v>3.22</v>
+        <v>5.3</v>
       </c>
       <c r="N119" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,16 +14627,16 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD119" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.9</v>
+        <v>4.02</v>
       </c>
       <c r="M121" t="n">
-        <v>3.55</v>
+        <v>3.41</v>
       </c>
       <c r="N121" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="M127" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="N127" t="n">
-        <v>4.12</v>
+        <v>3.51</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15585,10 +15585,10 @@
         <v>0</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD127" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.89</v>
+        <v>2.7</v>
       </c>
       <c r="M130" t="n">
-        <v>4</v>
+        <v>3.39</v>
       </c>
       <c r="N130" t="n">
-        <v>3.51</v>
+        <v>2.73</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15942,10 +15942,10 @@
         <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="M131" t="n">
-        <v>4.3</v>
+        <v>3.68</v>
       </c>
       <c r="N131" t="n">
-        <v>9.5</v>
+        <v>4.12</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="M153" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N153" t="n">
-        <v>4.12</v>
+        <v>3.55</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>4.33</v>
+        <v>1.7</v>
       </c>
       <c r="M154" t="n">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="N154" t="n">
-        <v>1.85</v>
+        <v>5.1</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,55 +18866,55 @@
         </is>
       </c>
       <c r="L155" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="M155" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N155" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="n">
+        <v>0</v>
+      </c>
+      <c r="V155" t="n">
+        <v>0</v>
+      </c>
+      <c r="W155" t="n">
+        <v>0</v>
+      </c>
+      <c r="X155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA155" t="n">
         <v>2.15</v>
       </c>
-      <c r="M155" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N155" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O155" t="n">
-        <v>0</v>
-      </c>
-      <c r="P155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0</v>
-      </c>
-      <c r="S155" t="n">
-        <v>0</v>
-      </c>
-      <c r="T155" t="n">
-        <v>0</v>
-      </c>
-      <c r="U155" t="n">
-        <v>0</v>
-      </c>
-      <c r="V155" t="n">
-        <v>0</v>
-      </c>
-      <c r="W155" t="n">
-        <v>0</v>
-      </c>
-      <c r="X155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA155" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AB155" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="M156" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N156" t="n">
-        <v>5.1</v>
+        <v>4.12</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,16 +19387,16 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD159" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.78</v>
+        <v>4.4</v>
       </c>
       <c r="M160" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N160" t="n">
-        <v>4.3</v>
+        <v>1.72</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,10 +19506,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AB160" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>4.4</v>
+        <v>1.78</v>
       </c>
       <c r="M161" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N161" t="n">
-        <v>1.72</v>
+        <v>4.3</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AB161" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,16 +19744,16 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB162" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC162" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD162" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>5.14</v>
+        <v>9.5</v>
       </c>
       <c r="M165" t="n">
-        <v>3.88</v>
+        <v>5.4</v>
       </c>
       <c r="N165" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20101,10 +20101,10 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AB165" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20702,10 +20702,10 @@
         <v>0</v>
       </c>
       <c r="AC170" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD170" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21059,10 +21059,10 @@
         <v>0</v>
       </c>
       <c r="AC173" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD173" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE173" t="n">
         <v>0</v>
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.51</v>
+        <v>2.32</v>
       </c>
       <c r="M174" t="n">
-        <v>4.69</v>
+        <v>3.13</v>
       </c>
       <c r="N174" t="n">
-        <v>5.97</v>
+        <v>3.44</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21410,10 +21410,10 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB176" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="M178" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="N178" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="M179" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="N179" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB179" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22362,10 +22362,10 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB184" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>6.9</v>
+        <v>5.3</v>
       </c>
       <c r="M188" t="n">
         <v>4.4</v>
       </c>
       <c r="N188" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22838,16 +22838,16 @@
         <v>0</v>
       </c>
       <c r="AA188" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB188" t="n">
-        <v>1.85</v>
+        <v>2.34</v>
       </c>
       <c r="AC188" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD188" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5.3</v>
+        <v>6.9</v>
       </c>
       <c r="M189" t="n">
         <v>4.4</v>
       </c>
       <c r="N189" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,16 +22957,16 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB189" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="AC189" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD189" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23076,10 +23076,10 @@
         <v>0</v>
       </c>
       <c r="AA190" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB190" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC190" t="n">
         <v>0</v>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23195,10 +23195,10 @@
         <v>0</v>
       </c>
       <c r="AA191" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB191" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC191" t="n">
         <v>0</v>

--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.65</v>
+        <v>4.33</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.91</v>
       </c>
       <c r="N33" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="M39" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="N39" t="n">
-        <v>2.73</v>
+        <v>4.9</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.11</v>
+        <v>1.34</v>
       </c>
       <c r="M47" t="n">
-        <v>3.34</v>
+        <v>4.77</v>
       </c>
       <c r="N47" t="n">
-        <v>2.09</v>
+        <v>6.92</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.34</v>
+        <v>3.11</v>
       </c>
       <c r="M48" t="n">
-        <v>4.77</v>
+        <v>3.34</v>
       </c>
       <c r="N48" t="n">
-        <v>6.92</v>
+        <v>2.09</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="N60" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="M65" t="n">
-        <v>3.53</v>
+        <v>3.35</v>
       </c>
       <c r="N65" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10587,10 +10587,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11182,10 +11182,10 @@
         <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD90" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="M93" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="N93" t="n">
-        <v>3.55</v>
+        <v>2.42</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="M98" t="n">
-        <v>3.46</v>
+        <v>3.75</v>
       </c>
       <c r="N98" t="n">
-        <v>2.32</v>
+        <v>5.7</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="M100" t="n">
-        <v>3.62</v>
+        <v>3.46</v>
       </c>
       <c r="N100" t="n">
-        <v>3.21</v>
+        <v>2.32</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="M102" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="N102" t="n">
-        <v>2.09</v>
+        <v>2.9</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="M106" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="N106" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="M107" t="n">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="N107" t="n">
-        <v>3.8</v>
+        <v>12</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="M109" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N109" t="n">
-        <v>2.35</v>
+        <v>3.55</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.59</v>
+        <v>1.7</v>
       </c>
       <c r="M111" t="n">
-        <v>3.32</v>
+        <v>4.1</v>
       </c>
       <c r="N111" t="n">
-        <v>2.36</v>
+        <v>4.5</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.73</v>
+        <v>3.9</v>
       </c>
       <c r="M117" t="n">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="N117" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>3.9</v>
+        <v>1.73</v>
       </c>
       <c r="M118" t="n">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="N118" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.25</v>
+        <v>4.02</v>
       </c>
       <c r="M119" t="n">
-        <v>5.3</v>
+        <v>3.41</v>
       </c>
       <c r="N119" t="n">
-        <v>12.5</v>
+        <v>1.85</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,16 +14627,16 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AC119" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>4.02</v>
+        <v>1.25</v>
       </c>
       <c r="M121" t="n">
-        <v>3.41</v>
+        <v>5.3</v>
       </c>
       <c r="N121" t="n">
-        <v>1.85</v>
+        <v>12.5</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.7</v>
+        <v>1.38</v>
       </c>
       <c r="M130" t="n">
-        <v>3.39</v>
+        <v>4.3</v>
       </c>
       <c r="N130" t="n">
-        <v>2.73</v>
+        <v>9.5</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="M153" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N153" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AB153" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="M154" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N154" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>4.33</v>
+        <v>1.99</v>
       </c>
       <c r="M155" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="N155" t="n">
-        <v>1.85</v>
+        <v>4.12</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AB155" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.99</v>
+        <v>4.33</v>
       </c>
       <c r="M156" t="n">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="N156" t="n">
-        <v>4.12</v>
+        <v>1.85</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,16 +19268,16 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC158" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD158" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE158" t="n">
         <v>0</v>
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,10 +19506,10 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC160" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1.25</v>
+        <v>4.4</v>
       </c>
       <c r="M162" t="n">
-        <v>6.1</v>
+        <v>4.1</v>
       </c>
       <c r="N162" t="n">
-        <v>11</v>
+        <v>1.72</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,16 +19744,16 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AB162" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC162" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD162" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20101,10 +20101,10 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB166" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB167" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.51</v>
+        <v>1.06</v>
       </c>
       <c r="M172" t="n">
-        <v>4.69</v>
+        <v>11.5</v>
       </c>
       <c r="N172" t="n">
-        <v>5.97</v>
+        <v>31</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AC172" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD172" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21059,10 +21059,10 @@
         <v>0</v>
       </c>
       <c r="AC173" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD173" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE173" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21410,10 +21410,10 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB176" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB177" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="M178" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="N178" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB178" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="M179" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="N179" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22362,10 +22362,10 @@
         <v>0</v>
       </c>
       <c r="AA184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB184" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="M185" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N185" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB185" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23076,10 +23076,10 @@
         <v>0</v>
       </c>
       <c r="AA190" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB190" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC190" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23314,10 +23314,10 @@
         <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB192" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>

--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="M40" t="n">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
       <c r="N40" t="n">
-        <v>4.23</v>
+        <v>4.9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="M60" t="n">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="N60" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AB60" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.85</v>
+        <v>2.93</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N61" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="M65" t="n">
-        <v>3.35</v>
+        <v>3.53</v>
       </c>
       <c r="N65" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="M79" t="n">
-        <v>3.75</v>
+        <v>4.01</v>
       </c>
       <c r="N79" t="n">
-        <v>2.79</v>
+        <v>5.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.81</v>
+        <v>2.65</v>
       </c>
       <c r="M85" t="n">
-        <v>4.17</v>
+        <v>2.81</v>
       </c>
       <c r="N85" t="n">
-        <v>4.01</v>
+        <v>2.65</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10587,10 +10587,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11301,10 +11301,10 @@
         <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD91" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE91" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="M93" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="N93" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.6</v>
+        <v>2.34</v>
       </c>
       <c r="M98" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="N98" t="n">
-        <v>5.7</v>
+        <v>3.21</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="M99" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N99" t="n">
-        <v>2.35</v>
+        <v>3.8</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="M105" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="N105" t="n">
-        <v>3.21</v>
+        <v>3.55</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="M106" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="N106" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AB106" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="M107" t="n">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="N107" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="M108" t="n">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="N108" t="n">
-        <v>3.8</v>
+        <v>12</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.7</v>
+        <v>2.59</v>
       </c>
       <c r="M111" t="n">
-        <v>4.1</v>
+        <v>3.32</v>
       </c>
       <c r="N111" t="n">
-        <v>4.5</v>
+        <v>2.36</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AB111" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.73</v>
+        <v>4.02</v>
       </c>
       <c r="M118" t="n">
-        <v>3.22</v>
+        <v>3.41</v>
       </c>
       <c r="N118" t="n">
-        <v>4.7</v>
+        <v>1.85</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>4.02</v>
+        <v>1.73</v>
       </c>
       <c r="M119" t="n">
-        <v>3.41</v>
+        <v>3.22</v>
       </c>
       <c r="N119" t="n">
-        <v>1.85</v>
+        <v>4.7</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.13</v>
+        <v>3.35</v>
       </c>
       <c r="M124" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="N124" t="n">
-        <v>3.76</v>
+        <v>2.15</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15466,10 +15466,10 @@
         <v>0</v>
       </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD126" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15585,10 +15585,10 @@
         <v>0</v>
       </c>
       <c r="AC127" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD127" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE127" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.82</v>
+        <v>1.38</v>
       </c>
       <c r="M129" t="n">
-        <v>3.68</v>
+        <v>4.3</v>
       </c>
       <c r="N129" t="n">
-        <v>4.12</v>
+        <v>9.5</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="M154" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N154" t="n">
-        <v>3.55</v>
+        <v>4.12</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AB154" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="M155" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N155" t="n">
-        <v>4.12</v>
+        <v>3.55</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AB155" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,16 +19268,16 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,10 +19387,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>4.4</v>
+        <v>1.25</v>
       </c>
       <c r="M162" t="n">
-        <v>4.1</v>
+        <v>6.1</v>
       </c>
       <c r="N162" t="n">
-        <v>1.72</v>
+        <v>11</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,16 +19744,16 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AB162" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AC162" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD162" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>5.14</v>
+        <v>9.5</v>
       </c>
       <c r="M167" t="n">
-        <v>3.88</v>
+        <v>5.4</v>
       </c>
       <c r="N167" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AB167" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,10 +20458,10 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AC172" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD172" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21053,10 +21053,10 @@
         <v>0</v>
       </c>
       <c r="AA173" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB173" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC173" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21416,10 +21416,10 @@
         <v>0</v>
       </c>
       <c r="AC176" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD176" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="M178" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="N178" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB178" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="M179" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="N179" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB179" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="M183" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N183" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB183" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22317,13 +22317,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB185" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5.3</v>
+        <v>6.9</v>
       </c>
       <c r="M188" t="n">
         <v>4.4</v>
       </c>
       <c r="N188" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22838,16 +22838,16 @@
         <v>0</v>
       </c>
       <c r="AA188" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB188" t="n">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="AC188" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD188" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>6.9</v>
+        <v>5.3</v>
       </c>
       <c r="M189" t="n">
         <v>4.4</v>
       </c>
       <c r="N189" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,16 +22957,16 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB189" t="n">
-        <v>1.85</v>
+        <v>2.34</v>
       </c>
       <c r="AC189" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD189" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE189" t="n">
         <v>0</v>

--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.34</v>
+        <v>3.11</v>
       </c>
       <c r="M47" t="n">
-        <v>4.77</v>
+        <v>3.34</v>
       </c>
       <c r="N47" t="n">
-        <v>6.92</v>
+        <v>2.09</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.11</v>
+        <v>1.34</v>
       </c>
       <c r="M49" t="n">
-        <v>3.34</v>
+        <v>4.77</v>
       </c>
       <c r="N49" t="n">
-        <v>2.09</v>
+        <v>6.92</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.6</v>
+        <v>2.93</v>
       </c>
       <c r="M60" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N60" t="n">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.93</v>
+        <v>2.6</v>
       </c>
       <c r="M61" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N61" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.85</v>
+        <v>2.17</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N62" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="M68" t="n">
-        <v>3.59</v>
+        <v>4.01</v>
       </c>
       <c r="N68" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10349,10 +10349,10 @@
         <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11301,10 +11301,10 @@
         <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE91" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="M93" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N93" t="n">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="M96" t="n">
-        <v>3.46</v>
+        <v>6.4</v>
       </c>
       <c r="N96" t="n">
-        <v>2.32</v>
+        <v>12</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.34</v>
+        <v>1.67</v>
       </c>
       <c r="M98" t="n">
-        <v>3.62</v>
+        <v>4.15</v>
       </c>
       <c r="N98" t="n">
-        <v>3.21</v>
+        <v>4.7</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="M99" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N99" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AB99" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.67</v>
+        <v>3.2</v>
       </c>
       <c r="M104" t="n">
-        <v>4.15</v>
+        <v>2.99</v>
       </c>
       <c r="N104" t="n">
-        <v>4.7</v>
+        <v>2.42</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="M105" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="N105" t="n">
-        <v>3.55</v>
+        <v>3.21</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,22 +14665,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.7</v>
+        <v>1.38</v>
       </c>
       <c r="M128" t="n">
-        <v>3.39</v>
+        <v>4.3</v>
       </c>
       <c r="N128" t="n">
-        <v>2.73</v>
+        <v>9.5</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="M153" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N153" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="M154" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N154" t="n">
-        <v>4.12</v>
+        <v>5.1</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,55 +18866,55 @@
         </is>
       </c>
       <c r="L155" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="M155" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N155" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="n">
+        <v>0</v>
+      </c>
+      <c r="V155" t="n">
+        <v>0</v>
+      </c>
+      <c r="W155" t="n">
+        <v>0</v>
+      </c>
+      <c r="X155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA155" t="n">
         <v>2.15</v>
       </c>
-      <c r="M155" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N155" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O155" t="n">
-        <v>0</v>
-      </c>
-      <c r="P155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0</v>
-      </c>
-      <c r="S155" t="n">
-        <v>0</v>
-      </c>
-      <c r="T155" t="n">
-        <v>0</v>
-      </c>
-      <c r="U155" t="n">
-        <v>0</v>
-      </c>
-      <c r="V155" t="n">
-        <v>0</v>
-      </c>
-      <c r="W155" t="n">
-        <v>0</v>
-      </c>
-      <c r="X155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA155" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AB155" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>4.33</v>
+        <v>1.99</v>
       </c>
       <c r="M156" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="N156" t="n">
-        <v>1.85</v>
+        <v>4.12</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,10 +19387,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,16 +19625,16 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB161" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC161" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD161" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,16 +19744,16 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD162" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB167" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB171" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AC172" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD172" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21053,10 +21053,10 @@
         <v>0</v>
       </c>
       <c r="AA173" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB173" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC173" t="n">
         <v>0</v>
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>2.32</v>
+        <v>1.51</v>
       </c>
       <c r="M174" t="n">
-        <v>3.13</v>
+        <v>4.69</v>
       </c>
       <c r="N174" t="n">
-        <v>3.44</v>
+        <v>5.97</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21416,10 +21416,10 @@
         <v>0</v>
       </c>
       <c r="AC176" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD176" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="M178" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="N178" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21648,10 +21648,10 @@
         <v>0</v>
       </c>
       <c r="AA178" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB178" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC178" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="M179" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="N179" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB185" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>

--- a/jogos_2026-02-01.xlsx
+++ b/jogos_2026-02-01.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.33</v>
+        <v>2.65</v>
       </c>
       <c r="M33" t="n">
-        <v>3.91</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Home United</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Home United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="M48" t="n">
-        <v>3.54</v>
+        <v>4.77</v>
       </c>
       <c r="N48" t="n">
-        <v>3.45</v>
+        <v>6.92</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
-        <v>4.77</v>
+        <v>3.54</v>
       </c>
       <c r="N49" t="n">
-        <v>6.92</v>
+        <v>3.45</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="M61" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N61" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="M62" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="M63" t="n">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="N64" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="M82" t="n">
-        <v>3.64</v>
+        <v>2.81</v>
       </c>
       <c r="N82" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.81</v>
+        <v>2.52</v>
       </c>
       <c r="M83" t="n">
-        <v>4.17</v>
+        <v>3.64</v>
       </c>
       <c r="N83" t="n">
-        <v>4.01</v>
+        <v>2.7</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10825,10 +10825,10 @@
         <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE87" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="M94" t="n">
         <v>3.75</v>
       </c>
       <c r="N94" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AB94" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="M96" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="N96" t="n">
-        <v>12</v>
+        <v>3.55</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="M98" t="n">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="N98" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB98" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="M104" t="n">
-        <v>2.99</v>
+        <v>3.28</v>
       </c>
       <c r="N104" t="n">
-        <v>2.42</v>
+        <v>2.09</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.6</v>
+        <v>2.34</v>
       </c>
       <c r="M109" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="N109" t="n">
-        <v>5.7</v>
+        <v>3.21</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB109" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.59</v>
+        <v>1.7</v>
       </c>
       <c r="M112" t="n">
-        <v>3.32</v>
+        <v>4.1</v>
       </c>
       <c r="N112" t="n">
-        <v>2.36</v>
+        <v>4.5</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,10 +13794,10 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>3.9</v>
+        <v>1.73</v>
       </c>
       <c r="M116" t="n">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="N116" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.73</v>
+        <v>4.02</v>
       </c>
       <c r="M117" t="n">
-        <v>3.22</v>
+        <v>3.41</v>
       </c>
       <c r="N117" t="n">
-        <v>4.7</v>
+        <v>1.85</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>4.02</v>
+        <v>3.9</v>
       </c>
       <c r="M118" t="n">
-        <v>3.41</v>
+        <v>3.55</v>
       </c>
       <c r="N118" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,16 +14627,16 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD119" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,16 +14865,16 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.13</v>
+        <v>3.35</v>
       </c>
       <c r="M123" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="N123" t="n">
-        <v>3.76</v>
+        <v>2.15</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.89</v>
+        <v>1.38</v>
       </c>
       <c r="M126" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N126" t="n">
-        <v>3.51</v>
+        <v>9.5</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,16 +15460,16 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC126" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD126" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE126" t="n">
         <v>0</v>
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="M127" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="N127" t="n">
-        <v>4.12</v>
+        <v>3.51</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15585,10 +15585,10 @@
         <v>0</v>
       </c>
       <c r="AC127" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD127" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </i